--- a/Config/Datas/Tables/j_技能战斗_SkillCombatConfig.xlsx
+++ b/Config/Datas/Tables/j_技能战斗_SkillCombatConfig.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TbSkillCombat" sheetId="1" r:id="R37381aab58dd4c7b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TbSkillCombat" sheetId="1" r:id="R2ac611bbdb964926"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -645,7 +645,7 @@
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="37">
+  <x:cellXfs count="38">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="49"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -752,6 +752,13 @@
     </x:xf>
     <x:xf numFmtId="0" fontId="26" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="49">
+      <x:extLst>
+        <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
+          <xfpb:xfComplement xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" i="0"/>
+        </x:ext>
+      </x:extLst>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="50">
@@ -989,6 +996,23 @@
 </x:styleSheet>
 </file>
 
+<file path=xl/featurePropertyBag/featurePropertyBag.xml><?xml version="1.0" encoding="utf-8"?>
+<xfpb:FeaturePropertyBags xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag">
+  <xfpb:bag type="Checkbox"/>
+  <xfpb:bag type="XFControls">
+    <xfpb:bagId k="CellControl">0</xfpb:bagId>
+  </xfpb:bag>
+  <xfpb:bag type="XFComplement">
+    <xfpb:bagId k="XFControls">1</xfpb:bagId>
+  </xfpb:bag>
+  <xfpb:bag type="XFComplements" extRef="XFComplementsMapperExtRef">
+    <xfpb:a k="MappedFeaturePropertyBags">
+      <xfpb:bagId>2</xfpb:bagId>
+    </xfpb:a>
+  </xfpb:bag>
+</xfpb:FeaturePropertyBags>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="ChatGPT">
   <a:themeElements>
@@ -1221,6 +1245,48 @@
       <x:c r="H1" s="24" t="str">
         <x:v>attackWindupSecondsMilli</x:v>
       </x:c>
+      <x:c r="I1" t="str">
+        <x:v>damagePermille</x:v>
+      </x:c>
+      <x:c r="J1" t="str">
+        <x:v>projectilePattern</x:v>
+      </x:c>
+      <x:c r="K1" t="str">
+        <x:v>projectileCount</x:v>
+      </x:c>
+      <x:c r="L1" t="str">
+        <x:v>spreadDegrees</x:v>
+      </x:c>
+      <x:c r="M1" t="str">
+        <x:v>pierceCount</x:v>
+      </x:c>
+      <x:c r="N1" t="str">
+        <x:v>chainCount</x:v>
+      </x:c>
+      <x:c r="O1" t="str">
+        <x:v>chainRangePixels</x:v>
+      </x:c>
+      <x:c r="P1" t="str">
+        <x:v>areaDurationMilli</x:v>
+      </x:c>
+      <x:c r="Q1" t="str">
+        <x:v>areaPulseIntervalMilli</x:v>
+      </x:c>
+      <x:c r="R1" t="str">
+        <x:v>areaFollowsOwner</x:v>
+      </x:c>
+      <x:c r="S1" t="str">
+        <x:v>impactRadiusPixels</x:v>
+      </x:c>
+      <x:c r="T1" t="str">
+        <x:v>areaRetargets</x:v>
+      </x:c>
+      <x:c r="U1" t="str">
+        <x:v>areaRingCount</x:v>
+      </x:c>
+      <x:c r="V1" t="str">
+        <x:v>areaRingWidthPixels</x:v>
+      </x:c>
     </x:row>
     <x:row r="2" ht="24" customHeight="1">
       <x:c r="A2" s="26" t="str">
@@ -1246,6 +1312,48 @@
       </x:c>
       <x:c r="H2" s="26" t="str">
         <x:v>int?</x:v>
+      </x:c>
+      <x:c r="I2" t="str">
+        <x:v>int</x:v>
+      </x:c>
+      <x:c r="J2" t="str">
+        <x:v>EProjectilePattern?</x:v>
+      </x:c>
+      <x:c r="K2" t="str">
+        <x:v>int</x:v>
+      </x:c>
+      <x:c r="L2" t="str">
+        <x:v>float</x:v>
+      </x:c>
+      <x:c r="M2" t="str">
+        <x:v>int</x:v>
+      </x:c>
+      <x:c r="N2" t="str">
+        <x:v>int</x:v>
+      </x:c>
+      <x:c r="O2" t="str">
+        <x:v>float</x:v>
+      </x:c>
+      <x:c r="P2" t="str">
+        <x:v>int</x:v>
+      </x:c>
+      <x:c r="Q2" t="str">
+        <x:v>int</x:v>
+      </x:c>
+      <x:c r="R2" t="str">
+        <x:v>bool</x:v>
+      </x:c>
+      <x:c r="S2" t="str">
+        <x:v>float</x:v>
+      </x:c>
+      <x:c r="T2" t="str">
+        <x:v>bool</x:v>
+      </x:c>
+      <x:c r="U2" t="str">
+        <x:v>int</x:v>
+      </x:c>
+      <x:c r="V2" t="str">
+        <x:v>float</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="22" customHeight="1">
@@ -1259,6 +1367,20 @@
       <x:c r="F3" s="28"/>
       <x:c r="G3" s="28"/>
       <x:c r="H3" s="28"/>
+      <x:c r="I3"/>
+      <x:c r="J3"/>
+      <x:c r="K3"/>
+      <x:c r="L3"/>
+      <x:c r="M3"/>
+      <x:c r="N3"/>
+      <x:c r="O3"/>
+      <x:c r="P3"/>
+      <x:c r="Q3"/>
+      <x:c r="R3"/>
+      <x:c r="S3"/>
+      <x:c r="T3"/>
+      <x:c r="U3"/>
+      <x:c r="V3"/>
     </x:row>
     <x:row r="4" ht="54" customHeight="1">
       <x:c r="A4" s="30" t="str">
@@ -1284,6 +1406,48 @@
       </x:c>
       <x:c r="H4" s="30" t="str">
         <x:v>普通近战 zd→gj 前摇秒数；弹丸留空；原单位×1000存整数，实际值=表值/1000，最多3位小数。</x:v>
+      </x:c>
+      <x:c r="I4" t="str">
+        <x:v>技能伤害千分比</x:v>
+      </x:c>
+      <x:c r="J4" t="str">
+        <x:v>弹丸阵型；非弹丸空</x:v>
+      </x:c>
+      <x:c r="K4" t="str">
+        <x:v>单次弹丸数；非弹丸0</x:v>
+      </x:c>
+      <x:c r="L4" t="str">
+        <x:v>扇形总夹角；其他阵型0</x:v>
+      </x:c>
+      <x:c r="M4" t="str">
+        <x:v>额外穿透数；同生命周期仅命中一次</x:v>
+      </x:c>
+      <x:c r="N4" t="str">
+        <x:v>额外跳转次数；与穿透互斥</x:v>
+      </x:c>
+      <x:c r="O4" t="str">
+        <x:v>连锁寻找未命中目标的范围</x:v>
+      </x:c>
+      <x:c r="P4" t="str">
+        <x:v>持续范围寿命毫秒；瞬时范围0</x:v>
+      </x:c>
+      <x:c r="Q4" t="str">
+        <x:v>持续范围脉冲间隔毫秒；瞬时0</x:v>
+      </x:c>
+      <x:c r="R4" t="str">
+        <x:v>范围以施法者为中心并跟随；否则固定目标位置</x:v>
+      </x:c>
+      <x:c r="S4" t="str">
+        <x:v>弹丸命中时爆发半径；0无爆发，与穿透连锁互斥</x:v>
+      </x:c>
+      <x:c r="T4" t="str">
+        <x:v>每次脉冲重新选取范围内未选过的目标落点</x:v>
+      </x:c>
+      <x:c r="U4" t="str">
+        <x:v>0为实心区域，正数为等距同心环数量</x:v>
+      </x:c>
+      <x:c r="V4" t="str">
+        <x:v>环带宽度；实心区域填0</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="25" customHeight="1">
@@ -1307,6 +1471,48 @@
         <x:v>10000</x:v>
       </x:c>
       <x:c r="H5" s="36"/>
+      <x:c r="I5" t="n">
+        <x:v>1000</x:v>
+      </x:c>
+      <x:c r="J5" t="str">
+        <x:v>Targeted</x:v>
+      </x:c>
+      <x:c r="K5" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="L5" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M5" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N5" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O5" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P5" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Q5" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="R5" s="37" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S5" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="T5" s="37" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="U5" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="V5" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="6" ht="25" customHeight="1">
       <x:c r="A6" s="36"/>
@@ -1327,6 +1533,46 @@
       <x:c r="H6" s="36" t="n">
         <x:v>200</x:v>
       </x:c>
+      <x:c r="I6" t="n">
+        <x:v>1000</x:v>
+      </x:c>
+      <x:c r="J6"/>
+      <x:c r="K6" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L6" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M6" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N6" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O6" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P6" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Q6" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="R6" s="37" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S6" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="T6" s="37" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="U6" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="V6" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="7">
       <x:c r="A7" s="36"/>
@@ -1345,6 +1591,776 @@
       <x:c r="F7" s="36"/>
       <x:c r="G7" s="36"/>
       <x:c r="H7" s="36"/>
+      <x:c r="I7" t="n">
+        <x:v>1000</x:v>
+      </x:c>
+      <x:c r="J7"/>
+      <x:c r="K7" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L7" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M7" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N7" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O7" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P7" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Q7" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="R7" s="37" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S7" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="T7" s="37" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="U7" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="V7" t="n">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8">
+      <x:c r="A8"/>
+      <x:c r="B8" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C8" t="str">
+        <x:v>Projectile</x:v>
+      </x:c>
+      <x:c r="D8" t="n">
+        <x:v>1300</x:v>
+      </x:c>
+      <x:c r="E8" t="n">
+        <x:v>600</x:v>
+      </x:c>
+      <x:c r="F8" t="n">
+        <x:v>1000</x:v>
+      </x:c>
+      <x:c r="G8" t="n">
+        <x:v>1500</x:v>
+      </x:c>
+      <x:c r="H8"/>
+      <x:c r="I8" t="n">
+        <x:v>650</x:v>
+      </x:c>
+      <x:c r="J8" t="str">
+        <x:v>Fan</x:v>
+      </x:c>
+      <x:c r="K8" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="L8" t="n">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="M8" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N8" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O8" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P8" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Q8" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="R8" s="37" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S8" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="T8" s="37" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="U8" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="V8" t="n">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9">
+      <x:c r="A9"/>
+      <x:c r="B9" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="C9" t="str">
+        <x:v>Projectile</x:v>
+      </x:c>
+      <x:c r="D9" t="n">
+        <x:v>1300</x:v>
+      </x:c>
+      <x:c r="E9" t="n">
+        <x:v>600</x:v>
+      </x:c>
+      <x:c r="F9" t="n">
+        <x:v>1100</x:v>
+      </x:c>
+      <x:c r="G9" t="n">
+        <x:v>2200</x:v>
+      </x:c>
+      <x:c r="H9"/>
+      <x:c r="I9" t="n">
+        <x:v>850</x:v>
+      </x:c>
+      <x:c r="J9" t="str">
+        <x:v>Targeted</x:v>
+      </x:c>
+      <x:c r="K9" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="L9" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M9" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N9" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="O9" t="n">
+        <x:v>280</x:v>
+      </x:c>
+      <x:c r="P9" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Q9" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="R9" s="37" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S9" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="T9" s="37" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="U9" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="V9" t="n">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10">
+      <x:c r="A10"/>
+      <x:c r="B10" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="C10" t="str">
+        <x:v>TargetArea</x:v>
+      </x:c>
+      <x:c r="D10" t="n">
+        <x:v>3000</x:v>
+      </x:c>
+      <x:c r="E10" t="n">
+        <x:v>600</x:v>
+      </x:c>
+      <x:c r="F10"/>
+      <x:c r="G10"/>
+      <x:c r="H10"/>
+      <x:c r="I10" t="n">
+        <x:v>450</x:v>
+      </x:c>
+      <x:c r="J10"/>
+      <x:c r="K10" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L10" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M10" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N10" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O10" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P10" t="n">
+        <x:v>2200</x:v>
+      </x:c>
+      <x:c r="Q10" t="n">
+        <x:v>600</x:v>
+      </x:c>
+      <x:c r="R10" s="37" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S10" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="T10" s="37" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="U10" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="V10" t="n">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11">
+      <x:c r="A11"/>
+      <x:c r="B11" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="C11" t="str">
+        <x:v>TargetArea</x:v>
+      </x:c>
+      <x:c r="D11" t="n">
+        <x:v>2200</x:v>
+      </x:c>
+      <x:c r="E11" t="n">
+        <x:v>360</x:v>
+      </x:c>
+      <x:c r="F11"/>
+      <x:c r="G11"/>
+      <x:c r="H11"/>
+      <x:c r="I11" t="n">
+        <x:v>400</x:v>
+      </x:c>
+      <x:c r="J11"/>
+      <x:c r="K11" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L11" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M11" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N11" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O11" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P11" t="n">
+        <x:v>2000</x:v>
+      </x:c>
+      <x:c r="Q11" t="n">
+        <x:v>650</x:v>
+      </x:c>
+      <x:c r="R11" s="37" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="S11" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="T11" s="37" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="U11" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="V11" t="n">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12">
+      <x:c r="A12"/>
+      <x:c r="B12" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="C12" t="str">
+        <x:v>Projectile</x:v>
+      </x:c>
+      <x:c r="D12" t="n">
+        <x:v>900</x:v>
+      </x:c>
+      <x:c r="E12" t="n">
+        <x:v>600</x:v>
+      </x:c>
+      <x:c r="F12" t="n">
+        <x:v>1400</x:v>
+      </x:c>
+      <x:c r="G12" t="n">
+        <x:v>1500</x:v>
+      </x:c>
+      <x:c r="H12"/>
+      <x:c r="I12" t="n">
+        <x:v>800</x:v>
+      </x:c>
+      <x:c r="J12" t="str">
+        <x:v>Radial</x:v>
+      </x:c>
+      <x:c r="K12" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="L12" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M12" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="N12" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O12" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P12" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Q12" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="R12" s="37" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S12" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="T12" s="37" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="U12" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="V12" t="n">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13">
+      <x:c r="A13"/>
+      <x:c r="B13" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="C13" t="str">
+        <x:v>Projectile</x:v>
+      </x:c>
+      <x:c r="D13" t="n">
+        <x:v>1200</x:v>
+      </x:c>
+      <x:c r="E13" t="n">
+        <x:v>650</x:v>
+      </x:c>
+      <x:c r="F13" t="n">
+        <x:v>1100</x:v>
+      </x:c>
+      <x:c r="G13" t="n">
+        <x:v>1800</x:v>
+      </x:c>
+      <x:c r="H13"/>
+      <x:c r="I13" t="n">
+        <x:v>850</x:v>
+      </x:c>
+      <x:c r="J13" t="str">
+        <x:v>Fan</x:v>
+      </x:c>
+      <x:c r="K13" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="L13" t="n">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="M13" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N13" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O13" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P13" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Q13" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="R13" s="37" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S13" t="n">
+        <x:v>120</x:v>
+      </x:c>
+      <x:c r="T13" s="37" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="U13" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="V13" t="n">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14">
+      <x:c r="A14"/>
+      <x:c r="B14" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="C14" t="str">
+        <x:v>TargetArea</x:v>
+      </x:c>
+      <x:c r="D14" t="n">
+        <x:v>1800</x:v>
+      </x:c>
+      <x:c r="E14" t="n">
+        <x:v>650</x:v>
+      </x:c>
+      <x:c r="F14"/>
+      <x:c r="G14"/>
+      <x:c r="H14"/>
+      <x:c r="I14" t="n">
+        <x:v>900</x:v>
+      </x:c>
+      <x:c r="J14"/>
+      <x:c r="K14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P14" t="n">
+        <x:v>900</x:v>
+      </x:c>
+      <x:c r="Q14" t="n">
+        <x:v>300</x:v>
+      </x:c>
+      <x:c r="R14" s="37" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="T14" s="37" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="U14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="V14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15">
+      <x:c r="A15"/>
+      <x:c r="B15" t="n">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="C15" t="str">
+        <x:v>TargetArea</x:v>
+      </x:c>
+      <x:c r="D15" t="n">
+        <x:v>4500</x:v>
+      </x:c>
+      <x:c r="E15" t="n">
+        <x:v>650</x:v>
+      </x:c>
+      <x:c r="F15"/>
+      <x:c r="G15"/>
+      <x:c r="H15"/>
+      <x:c r="I15" t="n">
+        <x:v>550</x:v>
+      </x:c>
+      <x:c r="J15"/>
+      <x:c r="K15" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L15" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M15" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N15" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O15" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P15" t="n">
+        <x:v>4000</x:v>
+      </x:c>
+      <x:c r="Q15" t="n">
+        <x:v>400</x:v>
+      </x:c>
+      <x:c r="R15" s="37" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S15" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="T15" s="37" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="U15" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="V15" t="n">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16">
+      <x:c r="A16"/>
+      <x:c r="B16" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="C16" t="str">
+        <x:v>TargetArea</x:v>
+      </x:c>
+      <x:c r="D16" t="n">
+        <x:v>3000</x:v>
+      </x:c>
+      <x:c r="E16" t="n">
+        <x:v>450</x:v>
+      </x:c>
+      <x:c r="F16"/>
+      <x:c r="G16"/>
+      <x:c r="H16"/>
+      <x:c r="I16" t="n">
+        <x:v>600</x:v>
+      </x:c>
+      <x:c r="J16"/>
+      <x:c r="K16" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L16" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M16" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N16" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O16" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P16" t="n">
+        <x:v>2800</x:v>
+      </x:c>
+      <x:c r="Q16" t="n">
+        <x:v>400</x:v>
+      </x:c>
+      <x:c r="R16" s="37" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="S16" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="T16" s="37" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="U16" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="V16" t="n">
+        <x:v>40</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17">
+      <x:c r="A17"/>
+      <x:c r="B17" t="n">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C17" t="str">
+        <x:v>Projectile</x:v>
+      </x:c>
+      <x:c r="D17" t="n">
+        <x:v>1100</x:v>
+      </x:c>
+      <x:c r="E17" t="n">
+        <x:v>650</x:v>
+      </x:c>
+      <x:c r="F17" t="n">
+        <x:v>1400</x:v>
+      </x:c>
+      <x:c r="G17" t="n">
+        <x:v>3200</x:v>
+      </x:c>
+      <x:c r="H17"/>
+      <x:c r="I17" t="n">
+        <x:v>1100</x:v>
+      </x:c>
+      <x:c r="J17" t="str">
+        <x:v>Targeted</x:v>
+      </x:c>
+      <x:c r="K17" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="L17" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M17" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N17" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="O17" t="n">
+        <x:v>420</x:v>
+      </x:c>
+      <x:c r="P17" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Q17" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="R17" s="37" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S17" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="T17" s="37" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="U17" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="V17" t="n">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18">
+      <x:c r="A18"/>
+      <x:c r="B18" t="n">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C18" t="str">
+        <x:v>Melee</x:v>
+      </x:c>
+      <x:c r="D18" t="n">
+        <x:v>850</x:v>
+      </x:c>
+      <x:c r="E18" t="n">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="F18"/>
+      <x:c r="G18"/>
+      <x:c r="H18" t="n">
+        <x:v>200</x:v>
+      </x:c>
+      <x:c r="I18" t="n">
+        <x:v>1000</x:v>
+      </x:c>
+      <x:c r="J18"/>
+      <x:c r="K18" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L18" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M18" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N18" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O18" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P18" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Q18" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="R18" s="37" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S18" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="T18" s="37" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="U18" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="V18" t="n">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19">
+      <x:c r="A19"/>
+      <x:c r="B19" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C19" t="str">
+        <x:v>Melee</x:v>
+      </x:c>
+      <x:c r="D19" t="n">
+        <x:v>2400</x:v>
+      </x:c>
+      <x:c r="E19" t="n">
+        <x:v>240</x:v>
+      </x:c>
+      <x:c r="F19"/>
+      <x:c r="G19"/>
+      <x:c r="H19" t="n">
+        <x:v>700</x:v>
+      </x:c>
+      <x:c r="I19" t="n">
+        <x:v>1000</x:v>
+      </x:c>
+      <x:c r="J19"/>
+      <x:c r="K19" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L19" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M19" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N19" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O19" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P19" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Q19" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="R19" s="37" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S19" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="T19" s="37" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="U19" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="V19" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
